--- a/validation/results/validation-results.xlsx
+++ b/validation/results/validation-results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="197">
   <si>
     <t>study_id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>note</t>
   </si>
   <si>
+    <t>scored_by_function</t>
+  </si>
+  <si>
     <t>A0</t>
   </si>
   <si>
@@ -517,7 +520,7 @@
     <t>agreement with stated answer</t>
   </si>
   <si>
-    <t>84.7-95.8</t>
+    <t>83.8-95.5</t>
   </si>
   <si>
     <t>checks excluded as INFO</t>
@@ -950,10 +953,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,31 +999,34 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>2020</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>1E-16</v>
@@ -1029,118 +1035,127 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>2020</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
       </c>
       <c r="C4">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>2016</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>0.252</v>
@@ -1149,39 +1164,42 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>38</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>2016</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>0.157</v>
@@ -1190,39 +1208,42 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>38</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>2016</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>0.438</v>
@@ -1231,39 +1252,42 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>38</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>2016</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.017</v>
@@ -1272,39 +1296,42 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>43</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>2016</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.004</v>
@@ -1313,77 +1340,83 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>45</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>2016</v>
       </c>
       <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
       </c>
       <c r="C11">
         <v>2016</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11">
         <v>0.674</v>
@@ -1392,39 +1425,42 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>38</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>2016</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
         <v>50</v>
       </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12">
         <v>0.092</v>
@@ -1433,39 +1469,42 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>38</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>2015</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13">
         <v>2E-07</v>
@@ -1474,39 +1513,42 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14">
         <v>2015</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14">
         <v>1.3E-07</v>
@@ -1515,39 +1557,42 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>2015</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15">
         <v>1.1E-05</v>
@@ -1556,39 +1601,42 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>2015</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16">
         <v>3.8E-05</v>
@@ -1597,39 +1645,42 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17">
         <v>2015</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17">
         <v>0.002</v>
@@ -1638,39 +1689,42 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <v>2015</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18">
         <v>0.005</v>
@@ -1679,39 +1733,42 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19">
         <v>2015</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19">
         <v>0.005</v>
@@ -1720,39 +1777,42 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20">
         <v>2015</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20">
         <v>0.153</v>
@@ -1761,39 +1821,42 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>65</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21">
         <v>2015</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21">
         <v>0.00065</v>
@@ -1802,144 +1865,156 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>69</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22">
         <v>2015</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>72</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>2015</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>76</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>79</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25">
         <v>2020</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25">
         <v>5.7E-05</v>
@@ -1948,39 +2023,42 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>83</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26">
         <v>2020</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I26">
         <v>0.008999999999999999</v>
@@ -1989,39 +2067,42 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>83</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C27">
         <v>2020</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27">
         <v>0.059</v>
@@ -2030,39 +2111,42 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>65</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>2020</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I28">
         <v>0.518</v>
@@ -2071,39 +2155,42 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>65</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29">
         <v>2020</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29">
         <v>0.004</v>
@@ -2112,42 +2199,45 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>88</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>2020</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I30">
         <v>0.465</v>
@@ -2156,39 +2246,42 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>91</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31">
         <v>2020</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I31">
         <v>0.662</v>
@@ -2197,109 +2290,118 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>91</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32">
         <v>2020</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+        <v>94</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>2020</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+        <v>97</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34">
         <v>2024</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34">
         <v>0.493</v>
@@ -2308,42 +2410,45 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>102</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I35">
         <v>0.955</v>
@@ -2352,109 +2457,118 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+        <v>104</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36">
         <v>2024</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+        <v>106</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C37">
         <v>2024</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+        <v>109</v>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38">
         <v>2020</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I38">
         <v>1.9E-09</v>
@@ -2463,39 +2577,42 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M38" t="b">
         <v>1</v>
       </c>
       <c r="N38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+        <v>113</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39">
         <v>2020</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I39">
         <v>0.001</v>
@@ -2504,147 +2621,159 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+        <v>115</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40">
         <v>2020</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>117</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41">
         <v>2020</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" t="s">
+        <v>75</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
         <v>117</v>
       </c>
-      <c r="F41" t="s">
-        <v>73</v>
-      </c>
-      <c r="G41" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" t="s">
-        <v>28</v>
-      </c>
-      <c r="L41" t="s">
-        <v>74</v>
-      </c>
-      <c r="M41" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42">
         <v>2020</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+        <v>120</v>
+      </c>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C43">
         <v>2019</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I43">
         <v>6.200000000000001E-11</v>
@@ -2653,39 +2782,42 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+        <v>124</v>
+      </c>
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44">
         <v>2019</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I44">
         <v>0.07099999999999999</v>
@@ -2694,42 +2826,45 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+        <v>126</v>
+      </c>
+      <c r="O44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C45">
         <v>2019</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I45">
         <v>0.148</v>
@@ -2738,39 +2873,42 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+        <v>128</v>
+      </c>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C46">
         <v>2019</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46">
         <v>0.001</v>
@@ -2779,112 +2917,121 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+        <v>130</v>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C47">
         <v>2019</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+        <v>132</v>
+      </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C48">
         <v>2019</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+        <v>134</v>
+      </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C49">
         <v>2017</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I49">
         <v>2.2E-07</v>
@@ -2893,39 +3040,42 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+        <v>138</v>
+      </c>
+      <c r="O49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C50">
         <v>2017</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I50">
         <v>0.001</v>
@@ -2934,112 +3084,121 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+        <v>140</v>
+      </c>
+      <c r="O50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C51">
         <v>2017</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+        <v>142</v>
+      </c>
+      <c r="O51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52">
         <v>2017</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>29</v>
+      </c>
+      <c r="L52" t="s">
+        <v>75</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
         <v>142</v>
       </c>
-      <c r="F52" t="s">
-        <v>73</v>
-      </c>
-      <c r="G52" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>28</v>
-      </c>
-      <c r="L52" t="s">
-        <v>74</v>
-      </c>
-      <c r="M52" t="b">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53">
         <v>2017</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I53">
         <v>0.21</v>
@@ -3048,42 +3207,45 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>147</v>
+      </c>
+      <c r="O53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C54">
         <v>2017</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I54">
         <v>0.001</v>
@@ -3092,42 +3254,45 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+        <v>149</v>
+      </c>
+      <c r="O54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55">
         <v>2017</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I55">
         <v>1.3E-05</v>
@@ -3136,118 +3301,130 @@
         <v>1</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+        <v>151</v>
+      </c>
+      <c r="O55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C56">
         <v>2017</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+        <v>153</v>
+      </c>
+      <c r="O56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C57">
         <v>2017</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+        <v>155</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C58">
         <v>2017</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3262,50 +3439,50 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D2">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>91.8</v>
+        <v>91.3</v>
       </c>
       <c r="F2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -3313,10 +3490,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3324,10 +3501,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -3335,10 +3512,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -3350,15 +3527,15 @@
         <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -3370,15 +3547,15 @@
         <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3390,7 +3567,7 @@
         <v>70.2</v>
       </c>
       <c r="F8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3411,21 +3588,21 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -3439,10 +3616,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -3456,10 +3633,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -3473,10 +3650,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -3490,10 +3667,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -3507,10 +3684,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -3524,10 +3701,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -3541,10 +3718,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -3558,10 +3735,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -3575,10 +3752,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3602,19 +3779,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3714,25 +3891,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3755,7 +3932,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3778,7 +3955,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3801,7 +3978,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3824,7 +4001,7 @@
         <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3847,7 +4024,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3870,7 +4047,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3893,7 +4070,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3916,7 +4093,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3931,46 +4108,46 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3991,15 +4168,15 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -4007,10 +4184,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -4018,10 +4195,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -4029,10 +4206,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -4040,10 +4217,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -4051,10 +4228,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -4062,10 +4239,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -4073,10 +4250,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -4084,10 +4261,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>3</v>

--- a/validation/results/validation-results.xlsx
+++ b/validation/results/validation-results.xlsx
@@ -13,14 +13,14 @@
     <sheet name="T3-threshold-sensitivity" sheetId="4" r:id="rId4"/>
     <sheet name="T4-coursework-by-set" sheetId="5" r:id="rId5"/>
     <sheet name="T5-coursework-causes" sheetId="6" r:id="rId6"/>
-    <sheet name="T6-vocabulary-crosswalk" sheetId="7" r:id="rId7"/>
+    <sheet name="T6-outside-the-denominator" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="201">
   <si>
     <t>study_id</t>
   </si>
@@ -43,9 +43,6 @@
     <t>claim_polarity</t>
   </si>
   <si>
-    <t>old_status</t>
-  </si>
-  <si>
     <t>p_value</t>
   </si>
   <si>
@@ -55,7 +52,7 @@
     <t>dispersion</t>
   </si>
   <si>
-    <t>new_status</t>
+    <t>status</t>
   </si>
   <si>
     <t>primary</t>
@@ -85,9 +82,6 @@
     <t>difference</t>
   </si>
   <si>
-    <t>held</t>
-  </si>
-  <si>
     <t>reproduced</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>beta</t>
   </si>
   <si>
-    <t>unadjudicated</t>
-  </si>
-  <si>
     <t>heterogeneous</t>
   </si>
   <si>
@@ -217,7 +208,7 @@
     <t>not_reproduced</t>
   </si>
   <si>
-    <t>RESCORED: right direction but not significant</t>
+    <t>direction agrees; not significant</t>
   </si>
   <si>
     <t>S3</t>
@@ -292,9 +283,6 @@
     <t>coprococcus-control</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>direction reversed but no significant difference</t>
   </si>
   <si>
@@ -334,7 +322,7 @@
     <t>lactobacillus-bps</t>
   </si>
   <si>
-    <t>RESCORED: direction only; no univariate evidence</t>
+    <t>direction agrees; no univariate evidence</t>
   </si>
   <si>
     <t>inter-animal-variation</t>
@@ -511,22 +499,28 @@
     <t>pct</t>
   </si>
   <si>
-    <t>ci_95_wilson</t>
+    <t>ci_95_clopper_pearson</t>
   </si>
   <si>
     <t>A: course material (verification)</t>
   </si>
   <si>
-    <t>agreement with stated answer</t>
-  </si>
-  <si>
-    <t>83.8-95.5</t>
-  </si>
-  <si>
-    <t>checks excluded as INFO</t>
-  </si>
-  <si>
-    <t>checks blocked by a guard</t>
+    <t>agreement per exercise question</t>
+  </si>
+  <si>
+    <t>65.5-93.2</t>
+  </si>
+  <si>
+    <t>agreement per row</t>
+  </si>
+  <si>
+    <t>83.6-96.2</t>
+  </si>
+  <si>
+    <t>checks with no expected value</t>
+  </si>
+  <si>
+    <t>checks refused by a guard</t>
   </si>
   <si>
     <t>checks with no input data</t>
@@ -535,22 +529,22 @@
     <t>B: published papers (reproducibility)</t>
   </si>
   <si>
-    <t>primary claim reproduced</t>
-  </si>
-  <si>
-    <t>72.2-100.0</t>
+    <t>designated headline claim reproduced</t>
+  </si>
+  <si>
+    <t>69.2-100.0</t>
   </si>
   <si>
     <t>scorable claims reproduced</t>
   </si>
   <si>
-    <t>59.8-85.8</t>
+    <t>58.8-87.3</t>
   </si>
   <si>
     <t>claims adjudicable</t>
   </si>
   <si>
-    <t>57.3-80.5</t>
+    <t>56.6-81.6</t>
   </si>
   <si>
     <t>scorable</t>
@@ -559,49 +553,64 @@
     <t>changed</t>
   </si>
   <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>DIFFER</t>
+  </si>
+  <si>
     <t>BLOCKED</t>
   </si>
   <si>
-    <t>DIFFER</t>
+    <t>NODATA</t>
   </si>
   <si>
     <t>INFO</t>
   </si>
   <si>
-    <t>MATCH</t>
-  </si>
-  <si>
-    <t>NODATA</t>
-  </si>
-  <si>
     <t>scored</t>
   </si>
   <si>
-    <t>agree</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>91%</t>
+    <t>agree_pct</t>
+  </si>
+  <si>
+    <t>ps10</t>
+  </si>
+  <si>
+    <t>ps11</t>
+  </si>
+  <si>
+    <t>ps12</t>
+  </si>
+  <si>
+    <t>ps13</t>
+  </si>
+  <si>
+    <t>ps7</t>
+  </si>
+  <si>
+    <t>ps9</t>
+  </si>
+  <si>
+    <t>quiz13</t>
+  </si>
+  <si>
+    <t>quiz9</t>
   </si>
   <si>
     <t>cause</t>
   </si>
   <si>
-    <t>n_checks</t>
-  </si>
-  <si>
-    <t>set</t>
+    <t>questions</t>
   </si>
   <si>
     <t>DESeq2 size factors: 1 of 51 taxa present in every sample</t>
   </si>
   <si>
-    <t>ps10</t>
+    <t>ps10 Q2, Q3a, Q3b, Q3c</t>
   </si>
   <si>
     <t>ps10 Q2 passes an object Q1 had overwritten with normalized counts</t>
@@ -610,7 +619,10 @@
     <t>Assumption check directs non-parametric; the question instructed ANOVA</t>
   </si>
   <si>
-    <t>ps7</t>
+    <t>ps7 Q6, Q8+</t>
+  </si>
+  <si>
+    <t>claims</t>
   </si>
 </sst>
 </file>
@@ -953,10 +965,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1">
+    <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -999,2431 +1011,2257 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
       </c>
       <c r="C2">
         <v>2020</v>
       </c>
       <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>1E-16</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
         <v>21</v>
       </c>
-      <c r="I2">
-        <v>1E-16</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
       </c>
       <c r="C3">
         <v>2020</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
       </c>
       <c r="C4">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="L4" t="s">
+      <c r="B5" t="s">
         <v>31</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
       </c>
       <c r="C5">
         <v>2016</v>
       </c>
       <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5">
+        <v>0.252</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5">
-        <v>0.252</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>2016</v>
       </c>
       <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <v>0.157</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6">
-        <v>0.157</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>2016</v>
       </c>
       <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>0.438</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>0.438</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>2016</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>0.017</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8">
-        <v>0.017</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>2016</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>0.004</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9">
-        <v>0.004</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>2016</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
         <v>20</v>
       </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>2016</v>
       </c>
       <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11">
+        <v>0.674</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11">
-        <v>0.674</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>2016</v>
       </c>
       <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12">
+        <v>0.092</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
         <v>50</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12">
-        <v>0.092</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
       </c>
       <c r="C13">
         <v>2015</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13">
+        <v>2E-07</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>20</v>
       </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13">
-        <v>2E-07</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>2015</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14">
+        <v>1.3E-07</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14">
-        <v>1.3E-07</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>57</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>2015</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15">
+        <v>1.1E-05</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15">
-        <v>1.1E-05</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>57</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C16">
         <v>2015</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16">
+        <v>3.8E-05</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="H16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16">
-        <v>3.8E-05</v>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>57</v>
-      </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C17">
         <v>2015</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17">
+        <v>0.002</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
         <v>20</v>
       </c>
-      <c r="H17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17">
-        <v>0.002</v>
-      </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>57</v>
-      </c>
-      <c r="O17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C18">
         <v>2015</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18">
+        <v>0.005</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
         <v>20</v>
       </c>
-      <c r="H18" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18">
-        <v>0.005</v>
-      </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>57</v>
-      </c>
-      <c r="O18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C19">
         <v>2015</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19">
+        <v>0.005</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
         <v>20</v>
       </c>
-      <c r="H19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19">
-        <v>0.005</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>57</v>
-      </c>
-      <c r="O19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>2015</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>0.153</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20">
-        <v>0.153</v>
-      </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="B21" t="s">
         <v>64</v>
-      </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
       </c>
       <c r="C21">
         <v>2015</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <v>0.00065</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>20</v>
       </c>
-      <c r="H21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21">
-        <v>0.00065</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>69</v>
-      </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C22">
         <v>2015</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" t="s">
-        <v>71</v>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K22" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>69</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C23">
         <v>2015</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
         <v>73</v>
       </c>
-      <c r="F23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" t="s">
-        <v>75</v>
-      </c>
-      <c r="M23" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>76</v>
-      </c>
-      <c r="O23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>76</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
         <v>77</v>
       </c>
-      <c r="F24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="B25" t="s">
         <v>78</v>
-      </c>
-      <c r="M24" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>79</v>
-      </c>
-      <c r="O24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
       </c>
       <c r="C25">
         <v>2020</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25">
+        <v>5.7E-05</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>20</v>
       </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25">
-        <v>5.7E-05</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" t="b">
-        <v>1</v>
-      </c>
-      <c r="N25" t="s">
-        <v>83</v>
-      </c>
-      <c r="O25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>80</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C26">
         <v>2020</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
         <v>20</v>
       </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="J26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>83</v>
-      </c>
-      <c r="O26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C27">
         <v>2020</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27">
+        <v>19</v>
+      </c>
+      <c r="H27">
         <v>0.059</v>
       </c>
-      <c r="J27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="s">
-        <v>64</v>
-      </c>
-      <c r="M27" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>65</v>
-      </c>
-      <c r="O27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C28">
         <v>2020</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28">
+        <v>19</v>
+      </c>
+      <c r="H28">
         <v>0.518</v>
       </c>
-      <c r="J28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>64</v>
-      </c>
-      <c r="M28" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>65</v>
-      </c>
-      <c r="O28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="s">
+        <v>62</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>2020</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29">
+        <v>0.004</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" t="s">
         <v>20</v>
       </c>
-      <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29">
-        <v>0.004</v>
-      </c>
-      <c r="J29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" t="s">
-        <v>87</v>
-      </c>
-      <c r="L29" t="s">
-        <v>22</v>
-      </c>
-      <c r="M29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>88</v>
-      </c>
-      <c r="O29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="s">
+        <v>85</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>2020</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" t="s">
-        <v>90</v>
-      </c>
-      <c r="I30">
+        <v>19</v>
+      </c>
+      <c r="H30">
         <v>0.465</v>
       </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>64</v>
-      </c>
-      <c r="M30" t="b">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>87</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C31">
         <v>2020</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" t="s">
-        <v>90</v>
-      </c>
-      <c r="I31">
+        <v>19</v>
+      </c>
+      <c r="H31">
         <v>0.662</v>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>64</v>
-      </c>
-      <c r="M31" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>91</v>
-      </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>87</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32">
         <v>2020</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>90</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" t="s">
         <v>78</v>
-      </c>
-      <c r="M32" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>94</v>
-      </c>
-      <c r="O32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
       </c>
       <c r="C33">
         <v>2020</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" t="s">
+        <v>92</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>93</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
         <v>95</v>
-      </c>
-      <c r="F33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" t="s">
-        <v>96</v>
-      </c>
-      <c r="M33" t="b">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>97</v>
-      </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
       </c>
       <c r="C34">
         <v>2024</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34">
+        <v>34</v>
+      </c>
+      <c r="H34">
         <v>0.493</v>
       </c>
-      <c r="J34" t="b">
-        <v>1</v>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
+        <v>84</v>
       </c>
       <c r="K34" t="s">
-        <v>87</v>
-      </c>
-      <c r="L34" t="s">
-        <v>22</v>
-      </c>
-      <c r="M34" t="b">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
-        <v>102</v>
-      </c>
-      <c r="O34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>98</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35">
+        <v>19</v>
+      </c>
+      <c r="H35">
         <v>0.955</v>
       </c>
-      <c r="J35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="s">
-        <v>64</v>
-      </c>
-      <c r="M35" t="b">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>104</v>
-      </c>
-      <c r="O35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>100</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C36">
         <v>2024</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" t="s">
-        <v>75</v>
-      </c>
-      <c r="M36" t="b">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>106</v>
-      </c>
-      <c r="O36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K36" t="s">
+        <v>72</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>102</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>2024</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="s">
+        <v>105</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="F37" t="s">
-        <v>74</v>
-      </c>
-      <c r="G37" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" t="s">
-        <v>108</v>
-      </c>
-      <c r="M37" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>109</v>
-      </c>
-      <c r="O37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="A38" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" t="s">
-        <v>111</v>
       </c>
       <c r="C38">
         <v>2020</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38">
+        <v>1.9E-09</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
         <v>20</v>
       </c>
-      <c r="H38" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38">
-        <v>1.9E-09</v>
-      </c>
-      <c r="J38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
-        <v>22</v>
-      </c>
-      <c r="M38" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" t="s">
-        <v>113</v>
-      </c>
-      <c r="O38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>109</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C39">
         <v>2020</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39">
+        <v>0.001</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
+        <v>84</v>
+      </c>
+      <c r="K39" t="s">
         <v>20</v>
       </c>
-      <c r="H39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39">
-        <v>0.001</v>
-      </c>
-      <c r="J39" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" t="s">
-        <v>22</v>
-      </c>
-      <c r="M39" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>115</v>
-      </c>
-      <c r="O39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
+        <v>111</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C40">
         <v>2020</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" t="s">
-        <v>29</v>
-      </c>
-      <c r="L40" t="s">
-        <v>75</v>
-      </c>
-      <c r="M40" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>117</v>
-      </c>
-      <c r="O40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K40" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
+        <v>113</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C41">
         <v>2020</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" t="s">
-        <v>29</v>
-      </c>
-      <c r="L41" t="s">
-        <v>75</v>
-      </c>
-      <c r="M41" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>117</v>
-      </c>
-      <c r="O41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K41" t="s">
+        <v>72</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>113</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C42">
         <v>2020</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" t="s">
-        <v>29</v>
-      </c>
-      <c r="L42" t="s">
-        <v>78</v>
-      </c>
-      <c r="M42" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>120</v>
-      </c>
-      <c r="O42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K42" t="s">
+        <v>75</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>116</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C43">
         <v>2019</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43">
+        <v>6.200000000000001E-11</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
         <v>20</v>
       </c>
-      <c r="H43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43">
-        <v>6.200000000000001E-11</v>
-      </c>
-      <c r="J43" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="s">
-        <v>22</v>
-      </c>
-      <c r="M43" t="b">
-        <v>1</v>
-      </c>
-      <c r="N43" t="s">
-        <v>124</v>
-      </c>
-      <c r="O43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>120</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C44">
         <v>2019</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>37</v>
-      </c>
-      <c r="H44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44">
+        <v>34</v>
+      </c>
+      <c r="H44">
         <v>0.07099999999999999</v>
       </c>
-      <c r="J44" t="b">
-        <v>1</v>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="s">
+        <v>84</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" t="b">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>126</v>
-      </c>
-      <c r="O44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>122</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C45">
         <v>2019</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" t="s">
-        <v>90</v>
-      </c>
-      <c r="I45">
+        <v>19</v>
+      </c>
+      <c r="H45">
         <v>0.148</v>
       </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>64</v>
-      </c>
-      <c r="M45" t="b">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>128</v>
-      </c>
-      <c r="O45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>124</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C46">
         <v>2019</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46">
+        <v>0.001</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" t="s">
         <v>28</v>
       </c>
-      <c r="G46" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46">
-        <v>0.001</v>
-      </c>
-      <c r="J46" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" t="s">
-        <v>30</v>
-      </c>
-      <c r="L46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M46" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>130</v>
-      </c>
-      <c r="O46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>126</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C47">
         <v>2019</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F47" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" t="s">
-        <v>29</v>
-      </c>
-      <c r="L47" t="s">
-        <v>75</v>
-      </c>
-      <c r="M47" t="b">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>132</v>
-      </c>
-      <c r="O47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>72</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>128</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C48">
         <v>2019</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F48" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" t="s">
-        <v>29</v>
-      </c>
-      <c r="L48" t="s">
-        <v>96</v>
-      </c>
-      <c r="M48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>134</v>
-      </c>
-      <c r="O48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>92</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>130</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C49">
         <v>2017</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49">
+        <v>2.2E-07</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
         <v>20</v>
       </c>
-      <c r="H49" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49">
-        <v>2.2E-07</v>
-      </c>
-      <c r="J49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="s">
-        <v>22</v>
-      </c>
-      <c r="M49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
-        <v>138</v>
-      </c>
-      <c r="O49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>134</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C50">
         <v>2017</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50">
+        <v>0.001</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>27</v>
+      </c>
+      <c r="K50" t="s">
         <v>28</v>
       </c>
-      <c r="G50" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" t="s">
-        <v>29</v>
-      </c>
-      <c r="I50">
-        <v>0.001</v>
-      </c>
-      <c r="J50" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" t="s">
-        <v>30</v>
-      </c>
-      <c r="L50" t="s">
-        <v>31</v>
-      </c>
-      <c r="M50" t="b">
-        <v>0</v>
-      </c>
-      <c r="N50" t="s">
-        <v>140</v>
-      </c>
-      <c r="O50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="s">
+        <v>136</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C51">
         <v>2017</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" t="s">
-        <v>29</v>
-      </c>
-      <c r="L51" t="s">
-        <v>75</v>
-      </c>
-      <c r="M51" t="b">
-        <v>0</v>
-      </c>
-      <c r="N51" t="s">
-        <v>142</v>
-      </c>
-      <c r="O51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>72</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>138</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C52">
         <v>2017</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G52" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" t="s">
-        <v>29</v>
-      </c>
-      <c r="L52" t="s">
-        <v>75</v>
-      </c>
-      <c r="M52" t="b">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
-        <v>142</v>
-      </c>
-      <c r="O52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
+        <v>138</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C53">
         <v>2017</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
-        <v>37</v>
-      </c>
-      <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53">
+        <v>34</v>
+      </c>
+      <c r="H53">
         <v>0.21</v>
       </c>
-      <c r="J53" t="b">
-        <v>1</v>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>84</v>
       </c>
       <c r="K53" t="s">
-        <v>87</v>
-      </c>
-      <c r="L53" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" t="b">
-        <v>1</v>
-      </c>
-      <c r="N53" t="s">
-        <v>147</v>
-      </c>
-      <c r="O53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>143</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C54">
         <v>2017</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54">
+        <v>0.001</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>84</v>
+      </c>
+      <c r="K54" t="s">
         <v>20</v>
       </c>
-      <c r="H54" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54">
-        <v>0.001</v>
-      </c>
-      <c r="J54" t="b">
-        <v>1</v>
-      </c>
-      <c r="K54" t="s">
-        <v>87</v>
-      </c>
-      <c r="L54" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" t="b">
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
-        <v>149</v>
-      </c>
-      <c r="O54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
+        <v>145</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C55">
         <v>2017</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55">
+        <v>1.3E-05</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
         <v>20</v>
       </c>
-      <c r="H55" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55">
-        <v>1.3E-05</v>
-      </c>
-      <c r="J55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" t="b">
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
-        <v>151</v>
-      </c>
-      <c r="O55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>147</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C56">
         <v>2017</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" t="s">
-        <v>29</v>
-      </c>
-      <c r="L56" t="s">
-        <v>71</v>
-      </c>
-      <c r="M56" t="b">
-        <v>0</v>
-      </c>
-      <c r="N56" t="s">
-        <v>153</v>
-      </c>
-      <c r="O56" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K56" t="s">
+        <v>68</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>149</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C57">
         <v>2017</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" t="s">
-        <v>29</v>
-      </c>
-      <c r="L57" t="s">
-        <v>108</v>
-      </c>
-      <c r="M57" t="b">
-        <v>0</v>
-      </c>
-      <c r="N57" t="s">
-        <v>155</v>
-      </c>
-      <c r="O57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>104</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
+        <v>151</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C58">
         <v>2017</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G58" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" t="s">
-        <v>29</v>
-      </c>
-      <c r="L58" t="s">
-        <v>108</v>
-      </c>
-      <c r="M58" t="b">
-        <v>0</v>
-      </c>
-      <c r="N58" t="s">
-        <v>157</v>
-      </c>
-      <c r="O58" t="b">
+        <v>19</v>
+      </c>
+      <c r="K58" t="s">
+        <v>104</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
+        <v>153</v>
+      </c>
+      <c r="N58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3434,140 +3272,160 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>91.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3">
+        <v>84</v>
+      </c>
+      <c r="D3">
+        <v>92</v>
+      </c>
+      <c r="E3">
+        <v>91.3</v>
+      </c>
+      <c r="F3" t="s">
         <v>164</v>
-      </c>
-      <c r="B3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
         <v>170</v>
-      </c>
-      <c r="B7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
         <v>40</v>
       </c>
-      <c r="D8">
+      <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9">
+        <v>40</v>
+      </c>
+      <c r="D9">
         <v>57</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>70.2</v>
       </c>
-      <c r="F8" t="s">
-        <v>176</v>
+      <c r="F9" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3588,21 +3446,21 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -3616,10 +3474,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -3633,10 +3491,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -3650,10 +3508,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -3667,10 +3525,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -3684,10 +3542,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -3701,10 +3559,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -3718,10 +3576,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -3735,10 +3593,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -3752,10 +3610,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3779,19 +3637,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3886,214 +3744,241 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>0</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>0</v>
-      </c>
       <c r="B3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>11</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>0</v>
-      </c>
       <c r="B4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>26</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>0</v>
+      <c r="H4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>188</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1</v>
+      <c r="H5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>189</v>
       </c>
       <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>23</v>
       </c>
-      <c r="G6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>0</v>
+      <c r="H6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>190</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>187</v>
+      <c r="H9">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4108,46 +3993,46 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -4157,116 +4042,54 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3">
+        <v>104</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>92</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>68</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
         <v>75</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10">
+      <c r="B6">
         <v>3</v>
       </c>
     </row>
